--- a/Tables/G_ProductInfoTable.xlsx
+++ b/Tables/G_ProductInfoTable.xlsx
@@ -383,11 +383,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.13"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
     <col customWidth="1" min="3" max="3" width="22.63"/>
-    <col customWidth="1" min="4" max="4" width="12.63"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
     <col customWidth="1" min="5" max="5" width="38.0"/>
-    <col customWidth="1" min="6" max="9" width="12.63"/>
+    <col customWidth="1" min="6" max="6" width="10.38"/>
+    <col customWidth="1" min="7" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6624,9 +6626,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="29.13"/>
-    <col customWidth="1" min="4" max="9" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="6" width="10.38"/>
+    <col customWidth="1" min="7" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12813,9 +12819,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="29.13"/>
-    <col customWidth="1" min="4" max="9" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="6" width="10.38"/>
+    <col customWidth="1" min="7" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19002,9 +19012,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="12.63"/>
-    <col customWidth="1" min="3" max="3" width="29.13"/>
-    <col customWidth="1" min="4" max="9" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="9.38"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="2.63"/>
+    <col customWidth="1" min="6" max="6" width="10.38"/>
+    <col customWidth="1" min="7" max="26" width="12.88"/>
   </cols>
   <sheetData>
     <row r="1">
